--- a/models/9433_DCF_Model_20260906.xlsx
+++ b/models/9433_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CDD478-5F4F-48D3-A001-0721CF917B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2D9307-C3E1-43D3-A296-660208ED01B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,7 +750,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 01:31, template rev 0d2e97a</t>
+    <t>Generated by pipeline on 2026-09-07 02:30, template rev 15b64f7</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -966,7 +966,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 01:31:32</t>
+    <t>2026-09-07 02:30:17</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1035,7 +1035,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>0d2e97a</t>
+    <t>15b64f7</t>
   </si>
   <si>
     <t>ticker</t>

--- a/models/9433_DCF_Model_20260906.xlsx
+++ b/models/9433_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2D9307-C3E1-43D3-A296-660208ED01B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A07748-FE45-4A06-B0F5-349335CC81B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,7 +750,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 02:30, template rev 15b64f7</t>
+    <t>Generated by pipeline on 2026-09-07 12:11, template rev 42941f3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -966,7 +966,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 02:30:17</t>
+    <t>2026-09-07 12:11:36</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1035,7 +1035,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>15b64f7</t>
+    <t>42941f3</t>
   </si>
   <si>
     <t>ticker</t>
